--- a/output/yearly_total_coral_cover_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_29_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.299427944145117</v>
+        <v>1.270338759668284</v>
       </c>
       <c r="C3" t="n">
-        <v>4.608566106477638</v>
+        <v>4.586103719004472</v>
       </c>
       <c r="D3" t="n">
-        <v>6.111178294591664</v>
+        <v>6.043967846758927</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01917234521442</v>
+        <v>11.90041032543168</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.497581792543484</v>
+        <v>1.411925075672744</v>
       </c>
       <c r="C4" t="n">
-        <v>5.059594544153112</v>
+        <v>4.986718247455892</v>
       </c>
       <c r="D4" t="n">
-        <v>6.343017550005912</v>
+        <v>6.279078722649362</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90019388670251</v>
+        <v>12.677722045778</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.752101297742237</v>
+        <v>1.611688875772825</v>
       </c>
       <c r="C5" t="n">
-        <v>5.64693151929278</v>
+        <v>5.451656249701741</v>
       </c>
       <c r="D5" t="n">
-        <v>6.740589980182644</v>
+        <v>6.555878196789726</v>
       </c>
       <c r="E5" t="n">
-        <v>14.13962279721766</v>
+        <v>13.61922332226429</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.028350347871267</v>
+        <v>1.847264215894616</v>
       </c>
       <c r="C6" t="n">
-        <v>6.358451252748969</v>
+        <v>5.9801944668756</v>
       </c>
       <c r="D6" t="n">
-        <v>7.098833743222915</v>
+        <v>6.877158733391911</v>
       </c>
       <c r="E6" t="n">
-        <v>15.48563534384315</v>
+        <v>14.70461741616213</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.342004958429956</v>
+        <v>2.120201049261763</v>
       </c>
       <c r="C7" t="n">
-        <v>7.26320151905704</v>
+        <v>6.575221146574252</v>
       </c>
       <c r="D7" t="n">
-        <v>7.510843356399811</v>
+        <v>7.244613285500507</v>
       </c>
       <c r="E7" t="n">
-        <v>17.11604983388681</v>
+        <v>15.94003548133652</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.508832863777481</v>
+        <v>1.342434327695391</v>
       </c>
       <c r="C8" t="n">
-        <v>5.002124831153623</v>
+        <v>4.101808263650636</v>
       </c>
       <c r="D8" t="n">
-        <v>5.731229895444597</v>
+        <v>5.460484936179027</v>
       </c>
       <c r="E8" t="n">
-        <v>12.2421875903757</v>
+        <v>10.90472752752505</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.915129410415703</v>
+        <v>1.712565621351782</v>
       </c>
       <c r="C9" t="n">
-        <v>6.209868181085824</v>
+        <v>4.798015358451599</v>
       </c>
       <c r="D9" t="n">
-        <v>6.290345781426288</v>
+        <v>5.896503740475064</v>
       </c>
       <c r="E9" t="n">
-        <v>14.41534337292781</v>
+        <v>12.40708472027844</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.343824169753951</v>
+        <v>2.125757604979694</v>
       </c>
       <c r="C10" t="n">
-        <v>7.557141939001987</v>
+        <v>5.651031726503082</v>
       </c>
       <c r="D10" t="n">
-        <v>6.808918303967261</v>
+        <v>6.379542780279571</v>
       </c>
       <c r="E10" t="n">
-        <v>16.7098844127232</v>
+        <v>14.15633211176235</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.783127868086116</v>
+        <v>2.559504523276221</v>
       </c>
       <c r="C11" t="n">
-        <v>8.9875706686156</v>
+        <v>6.655475058745255</v>
       </c>
       <c r="D11" t="n">
-        <v>7.286600937007083</v>
+        <v>6.896583615800083</v>
       </c>
       <c r="E11" t="n">
-        <v>19.0572994737088</v>
+        <v>16.11156319782156</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.213638835615735</v>
+        <v>3.038223924474513</v>
       </c>
       <c r="C12" t="n">
-        <v>10.43618926460345</v>
+        <v>7.772774351331922</v>
       </c>
       <c r="D12" t="n">
-        <v>7.825583445945711</v>
+        <v>7.341297614932317</v>
       </c>
       <c r="E12" t="n">
-        <v>21.4754115461649</v>
+        <v>18.15229589073875</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.618987832375987</v>
+        <v>3.527273060121577</v>
       </c>
       <c r="C13" t="n">
-        <v>11.91860000858773</v>
+        <v>8.983705244169203</v>
       </c>
       <c r="D13" t="n">
-        <v>8.367949549773655</v>
+        <v>7.927402764799416</v>
       </c>
       <c r="E13" t="n">
-        <v>23.90553739073738</v>
+        <v>20.43838106909019</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.07769230145161</v>
+        <v>2.061071312818711</v>
       </c>
       <c r="C14" t="n">
-        <v>8.261377478805782</v>
+        <v>6.46593764232513</v>
       </c>
       <c r="D14" t="n">
-        <v>6.338516607790937</v>
+        <v>6.065757643120045</v>
       </c>
       <c r="E14" t="n">
-        <v>16.67758638804833</v>
+        <v>14.59276659826389</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.137441466732071</v>
+        <v>2.180962342461332</v>
       </c>
       <c r="C15" t="n">
-        <v>8.870728643877694</v>
+        <v>6.924561082364028</v>
       </c>
       <c r="D15" t="n">
-        <v>6.385836847135633</v>
+        <v>6.097949150342298</v>
       </c>
       <c r="E15" t="n">
-        <v>17.3940069577454</v>
+        <v>15.20347257516766</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.485471027887565</v>
+        <v>2.607502267525444</v>
       </c>
       <c r="C16" t="n">
-        <v>10.46325104736757</v>
+        <v>8.197779862524674</v>
       </c>
       <c r="D16" t="n">
-        <v>6.951029000470522</v>
+        <v>6.602822724728263</v>
       </c>
       <c r="E16" t="n">
-        <v>19.89975107572566</v>
+        <v>17.40810485477838</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.988677237107552</v>
+        <v>2.133347578805362</v>
       </c>
       <c r="C17" t="n">
-        <v>9.649794534582748</v>
+        <v>7.649758476537062</v>
       </c>
       <c r="D17" t="n">
-        <v>6.489097070668313</v>
+        <v>6.16661258477732</v>
       </c>
       <c r="E17" t="n">
-        <v>18.12756884235861</v>
+        <v>15.94971864011974</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.27542610656396</v>
+        <v>2.513529377274939</v>
       </c>
       <c r="C18" t="n">
-        <v>11.26973715145224</v>
+        <v>8.911755880438166</v>
       </c>
       <c r="D18" t="n">
-        <v>6.942301263379768</v>
+        <v>6.599906934046651</v>
       </c>
       <c r="E18" t="n">
-        <v>20.48746452139597</v>
+        <v>18.02519219175976</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.290653013456828</v>
+        <v>2.606952488811065</v>
       </c>
       <c r="C19" t="n">
-        <v>12.07328782990121</v>
+        <v>9.57008643847495</v>
       </c>
       <c r="D19" t="n">
-        <v>7.074699758774492</v>
+        <v>6.726572022848574</v>
       </c>
       <c r="E19" t="n">
-        <v>21.43864060213253</v>
+        <v>18.90361095013459</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.560898704004848</v>
+        <v>2.983963242195925</v>
       </c>
       <c r="C20" t="n">
-        <v>13.86540935914151</v>
+        <v>11.06081142251148</v>
       </c>
       <c r="D20" t="n">
-        <v>7.632352089740767</v>
+        <v>7.155271792862028</v>
       </c>
       <c r="E20" t="n">
-        <v>24.05866015288712</v>
+        <v>21.20004645756943</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.529317486290469</v>
+        <v>1.82375344027113</v>
       </c>
       <c r="C21" t="n">
-        <v>10.18767446678549</v>
+        <v>8.201068717333902</v>
       </c>
       <c r="D21" t="n">
-        <v>6.409015910432901</v>
+        <v>5.958590063724464</v>
       </c>
       <c r="E21" t="n">
-        <v>18.12600786350886</v>
+        <v>15.9834122213295</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_29_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.270338759668284</v>
+        <v>1.249152644210638</v>
       </c>
       <c r="C3" t="n">
-        <v>4.586103719004472</v>
+        <v>4.651321218997587</v>
       </c>
       <c r="D3" t="n">
-        <v>6.043967846758927</v>
+        <v>6.117716734301948</v>
       </c>
       <c r="E3" t="n">
-        <v>11.90041032543168</v>
+        <v>12.01819059751017</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.411925075672744</v>
+        <v>1.3707499748865</v>
       </c>
       <c r="C4" t="n">
-        <v>4.986718247455892</v>
+        <v>5.187202991613749</v>
       </c>
       <c r="D4" t="n">
-        <v>6.279078722649362</v>
+        <v>6.388060154471421</v>
       </c>
       <c r="E4" t="n">
-        <v>12.677722045778</v>
+        <v>12.94601312097167</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.611688875772825</v>
+        <v>1.531071930265125</v>
       </c>
       <c r="C5" t="n">
-        <v>5.451656249701741</v>
+        <v>5.896729033445344</v>
       </c>
       <c r="D5" t="n">
-        <v>6.555878196789726</v>
+        <v>6.746282325957797</v>
       </c>
       <c r="E5" t="n">
-        <v>13.61922332226429</v>
+        <v>14.17408328966827</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.847264215894616</v>
+        <v>1.719290076399232</v>
       </c>
       <c r="C6" t="n">
-        <v>5.9801944668756</v>
+        <v>6.748255292412287</v>
       </c>
       <c r="D6" t="n">
-        <v>6.877158733391911</v>
+        <v>7.249979641855709</v>
       </c>
       <c r="E6" t="n">
-        <v>14.70461741616213</v>
+        <v>15.71752501066723</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.120201049261763</v>
+        <v>1.93136469187671</v>
       </c>
       <c r="C7" t="n">
-        <v>6.575221146574252</v>
+        <v>7.790005023337111</v>
       </c>
       <c r="D7" t="n">
-        <v>7.244613285500507</v>
+        <v>7.730861282965919</v>
       </c>
       <c r="E7" t="n">
-        <v>15.94003548133652</v>
+        <v>17.45223099817974</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.342434327695391</v>
+        <v>1.154401802003285</v>
       </c>
       <c r="C8" t="n">
-        <v>4.101808263650636</v>
+        <v>5.470071361689246</v>
       </c>
       <c r="D8" t="n">
-        <v>5.460484936179027</v>
+        <v>5.972836462283224</v>
       </c>
       <c r="E8" t="n">
-        <v>10.90472752752505</v>
+        <v>12.59730962597576</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.712565621351782</v>
+        <v>1.434363513790194</v>
       </c>
       <c r="C9" t="n">
-        <v>4.798015358451599</v>
+        <v>6.800897228150247</v>
       </c>
       <c r="D9" t="n">
-        <v>5.896503740475064</v>
+        <v>6.606750214636108</v>
       </c>
       <c r="E9" t="n">
-        <v>12.40708472027844</v>
+        <v>14.84201095657655</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.125757604979694</v>
+        <v>1.71839929041355</v>
       </c>
       <c r="C10" t="n">
-        <v>5.651031726503082</v>
+        <v>8.284520091572418</v>
       </c>
       <c r="D10" t="n">
-        <v>6.379542780279571</v>
+        <v>7.174455144121774</v>
       </c>
       <c r="E10" t="n">
-        <v>14.15633211176235</v>
+        <v>17.17737452610774</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.559504523276221</v>
+        <v>2.004932929194926</v>
       </c>
       <c r="C11" t="n">
-        <v>6.655475058745255</v>
+        <v>9.851680821200359</v>
       </c>
       <c r="D11" t="n">
-        <v>6.896583615800083</v>
+        <v>7.832322229723845</v>
       </c>
       <c r="E11" t="n">
-        <v>16.11156319782156</v>
+        <v>19.68893598011913</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.038223924474513</v>
+        <v>2.274455401295242</v>
       </c>
       <c r="C12" t="n">
-        <v>7.772774351331922</v>
+        <v>11.45928790739002</v>
       </c>
       <c r="D12" t="n">
-        <v>7.341297614932317</v>
+        <v>8.358033145551808</v>
       </c>
       <c r="E12" t="n">
-        <v>18.15229589073875</v>
+        <v>22.09177645423707</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.527273060121577</v>
+        <v>2.525553522095847</v>
       </c>
       <c r="C13" t="n">
-        <v>8.983705244169203</v>
+        <v>13.04263003282844</v>
       </c>
       <c r="D13" t="n">
-        <v>7.927402764799416</v>
+        <v>8.837923168014402</v>
       </c>
       <c r="E13" t="n">
-        <v>20.43838106909019</v>
+        <v>24.40610672293868</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.061071312818711</v>
+        <v>1.450856209767064</v>
       </c>
       <c r="C14" t="n">
-        <v>6.46593764232513</v>
+        <v>9.043781311705278</v>
       </c>
       <c r="D14" t="n">
-        <v>6.065757643120045</v>
+        <v>6.696069121677625</v>
       </c>
       <c r="E14" t="n">
-        <v>14.59276659826389</v>
+        <v>17.19070664314997</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180962342461332</v>
+        <v>1.465278083542449</v>
       </c>
       <c r="C15" t="n">
-        <v>6.924561082364028</v>
+        <v>9.697566377871398</v>
       </c>
       <c r="D15" t="n">
-        <v>6.097949150342298</v>
+        <v>6.74727708193114</v>
       </c>
       <c r="E15" t="n">
-        <v>15.20347257516766</v>
+        <v>17.91012154334499</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.607502267525444</v>
+        <v>1.692356327534737</v>
       </c>
       <c r="C16" t="n">
-        <v>8.197779862524674</v>
+        <v>11.41458420773682</v>
       </c>
       <c r="D16" t="n">
-        <v>6.602822724728263</v>
+        <v>7.297369955574712</v>
       </c>
       <c r="E16" t="n">
-        <v>17.40810485477838</v>
+        <v>20.40431049084626</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.133347578805362</v>
+        <v>1.353908623972691</v>
       </c>
       <c r="C17" t="n">
-        <v>7.649758476537062</v>
+        <v>10.46799288877908</v>
       </c>
       <c r="D17" t="n">
-        <v>6.16661258477732</v>
+        <v>6.807526938540766</v>
       </c>
       <c r="E17" t="n">
-        <v>15.94971864011974</v>
+        <v>18.62942845129254</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.513529377274939</v>
+        <v>1.538290660307285</v>
       </c>
       <c r="C18" t="n">
-        <v>8.911755880438166</v>
+        <v>12.20494019704071</v>
       </c>
       <c r="D18" t="n">
-        <v>6.599906934046651</v>
+        <v>7.312302338156305</v>
       </c>
       <c r="E18" t="n">
-        <v>18.02519219175976</v>
+        <v>21.0555331955043</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.606952488811065</v>
+        <v>1.535669393936946</v>
       </c>
       <c r="C19" t="n">
-        <v>9.57008643847495</v>
+        <v>13.04651396407516</v>
       </c>
       <c r="D19" t="n">
-        <v>6.726572022848574</v>
+        <v>7.42719627198431</v>
       </c>
       <c r="E19" t="n">
-        <v>18.90361095013459</v>
+        <v>22.00937962999642</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.983963242195925</v>
+        <v>1.699680165408418</v>
       </c>
       <c r="C20" t="n">
-        <v>11.06081142251148</v>
+        <v>14.95674955961339</v>
       </c>
       <c r="D20" t="n">
-        <v>7.155271792862028</v>
+        <v>7.932305465819294</v>
       </c>
       <c r="E20" t="n">
-        <v>21.20004645756943</v>
+        <v>24.5887351908411</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.82375344027113</v>
+        <v>1.009187552580509</v>
       </c>
       <c r="C21" t="n">
-        <v>8.201068717333902</v>
+        <v>10.98288028974837</v>
       </c>
       <c r="D21" t="n">
-        <v>5.958590063724464</v>
+        <v>6.645086963396088</v>
       </c>
       <c r="E21" t="n">
-        <v>15.9834122213295</v>
+        <v>18.63715480572496</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_29_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249152644210638</v>
+        <v>2.591882183434406</v>
       </c>
       <c r="C3" t="n">
-        <v>4.651321218997587</v>
+        <v>7.712901658230723</v>
       </c>
       <c r="D3" t="n">
-        <v>6.117716734301948</v>
+        <v>8.135898109783419</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01819059751017</v>
+        <v>18.44068195144855</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.3707499748865</v>
+        <v>1.060863318074831</v>
       </c>
       <c r="C4" t="n">
-        <v>5.187202991613749</v>
+        <v>4.531721268216062</v>
       </c>
       <c r="D4" t="n">
-        <v>6.388060154471421</v>
+        <v>5.635585677138208</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94601312097167</v>
+        <v>11.2281702634291</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.531071930265125</v>
+        <v>1.135716746116603</v>
       </c>
       <c r="C5" t="n">
-        <v>5.896729033445344</v>
+        <v>5.267569339708433</v>
       </c>
       <c r="D5" t="n">
-        <v>6.746282325957797</v>
+        <v>5.857053278445917</v>
       </c>
       <c r="E5" t="n">
-        <v>14.17408328966827</v>
+        <v>12.26033936427095</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.719290076399232</v>
+        <v>1.214629882508349</v>
       </c>
       <c r="C6" t="n">
-        <v>6.748255292412287</v>
+        <v>6.209043443676945</v>
       </c>
       <c r="D6" t="n">
-        <v>7.249979641855709</v>
+        <v>6.167900611405583</v>
       </c>
       <c r="E6" t="n">
-        <v>15.71752501066723</v>
+        <v>13.59157393759088</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.93136469187671</v>
+        <v>1.298935568849521</v>
       </c>
       <c r="C7" t="n">
-        <v>7.790005023337111</v>
+        <v>7.347650872291301</v>
       </c>
       <c r="D7" t="n">
-        <v>7.730861282965919</v>
+        <v>6.552119570020802</v>
       </c>
       <c r="E7" t="n">
-        <v>17.45223099817974</v>
+        <v>15.19870601116162</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.154401802003285</v>
+        <v>1.391139715775639</v>
       </c>
       <c r="C8" t="n">
-        <v>5.470071361689246</v>
+        <v>8.60222536246031</v>
       </c>
       <c r="D8" t="n">
-        <v>5.972836462283224</v>
+        <v>6.89808906023349</v>
       </c>
       <c r="E8" t="n">
-        <v>12.59730962597576</v>
+        <v>16.89145413846944</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.434363513790194</v>
+        <v>1.473801998970436</v>
       </c>
       <c r="C9" t="n">
-        <v>6.800897228150247</v>
+        <v>9.95342192468425</v>
       </c>
       <c r="D9" t="n">
-        <v>6.606750214636108</v>
+        <v>7.234263916752263</v>
       </c>
       <c r="E9" t="n">
-        <v>14.84201095657655</v>
+        <v>18.66148784040695</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.71839929041355</v>
+        <v>0.9461397150137786</v>
       </c>
       <c r="C10" t="n">
-        <v>8.284520091572418</v>
+        <v>7.20078561643091</v>
       </c>
       <c r="D10" t="n">
-        <v>7.174455144121774</v>
+        <v>5.715293347658019</v>
       </c>
       <c r="E10" t="n">
-        <v>17.17737452610774</v>
+        <v>13.86221867910271</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.004932929194926</v>
+        <v>0.8631231291426682</v>
       </c>
       <c r="C11" t="n">
-        <v>9.851680821200359</v>
+        <v>7.673477501071665</v>
       </c>
       <c r="D11" t="n">
-        <v>7.832322229723845</v>
+        <v>5.539845215432072</v>
       </c>
       <c r="E11" t="n">
-        <v>19.68893598011913</v>
+        <v>14.07644584564641</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.274455401295242</v>
+        <v>0.9089609294539518</v>
       </c>
       <c r="C12" t="n">
-        <v>11.45928790739002</v>
+        <v>9.096275361451355</v>
       </c>
       <c r="D12" t="n">
-        <v>8.358033145551808</v>
+        <v>5.903847811735662</v>
       </c>
       <c r="E12" t="n">
-        <v>22.09177645423707</v>
+        <v>15.90908410264097</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.525553522095847</v>
+        <v>0.7037658417893261</v>
       </c>
       <c r="C13" t="n">
-        <v>13.04263003282844</v>
+        <v>8.675115413806516</v>
       </c>
       <c r="D13" t="n">
-        <v>8.837923168014402</v>
+        <v>5.368265169160857</v>
       </c>
       <c r="E13" t="n">
-        <v>24.40610672293868</v>
+        <v>14.7471464247567</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.450856209767064</v>
+        <v>0.7492502129270808</v>
       </c>
       <c r="C14" t="n">
-        <v>9.043781311705278</v>
+        <v>10.23043939678248</v>
       </c>
       <c r="D14" t="n">
-        <v>6.696069121677625</v>
+        <v>5.698201120127081</v>
       </c>
       <c r="E14" t="n">
-        <v>17.19070664314997</v>
+        <v>16.67789072983664</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.465278083542449</v>
+        <v>0.7139760179134929</v>
       </c>
       <c r="C15" t="n">
-        <v>9.697566377871398</v>
+        <v>11.10777823268264</v>
       </c>
       <c r="D15" t="n">
-        <v>6.74727708193114</v>
+        <v>5.742252139616636</v>
       </c>
       <c r="E15" t="n">
-        <v>17.91012154334499</v>
+        <v>17.56400639021277</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.692356327534737</v>
+        <v>0.7729790549387262</v>
       </c>
       <c r="C16" t="n">
-        <v>11.41458420773682</v>
+        <v>13.01011075920169</v>
       </c>
       <c r="D16" t="n">
-        <v>7.297369955574712</v>
+        <v>6.145563913998269</v>
       </c>
       <c r="E16" t="n">
-        <v>20.40431049084626</v>
+        <v>19.92865372813868</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.353908623972691</v>
+        <v>0.4672824547903544</v>
       </c>
       <c r="C17" t="n">
-        <v>10.46799288877908</v>
+        <v>9.754674641827435</v>
       </c>
       <c r="D17" t="n">
-        <v>6.807526938540766</v>
+        <v>5.106914112813313</v>
       </c>
       <c r="E17" t="n">
-        <v>18.62942845129254</v>
+        <v>15.3288712094311</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.538290660307285</v>
+        <v>0.3550785096719864</v>
       </c>
       <c r="C18" t="n">
-        <v>12.20494019704071</v>
+        <v>8.719892926597213</v>
       </c>
       <c r="D18" t="n">
-        <v>7.312302338156305</v>
+        <v>4.649282237955705</v>
       </c>
       <c r="E18" t="n">
-        <v>21.0555331955043</v>
+        <v>13.7242536742249</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.535669393936946</v>
+        <v>0.4131488863781853</v>
       </c>
       <c r="C19" t="n">
-        <v>13.04651396407516</v>
+        <v>10.84471893532971</v>
       </c>
       <c r="D19" t="n">
-        <v>7.42719627198431</v>
+        <v>5.116643232562399</v>
       </c>
       <c r="E19" t="n">
-        <v>22.00937962999642</v>
+        <v>16.3745110542703</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.699680165408418</v>
+        <v>0.4656134836931348</v>
       </c>
       <c r="C20" t="n">
-        <v>14.95674955961339</v>
+        <v>13.1392694871724</v>
       </c>
       <c r="D20" t="n">
-        <v>7.932305465819294</v>
+        <v>5.571722563388965</v>
       </c>
       <c r="E20" t="n">
-        <v>24.5887351908411</v>
+        <v>19.1766055342545</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.009187552580509</v>
+        <v>0.5101455595577702</v>
       </c>
       <c r="C21" t="n">
-        <v>10.98288028974837</v>
+        <v>15.4533568183296</v>
       </c>
       <c r="D21" t="n">
-        <v>6.645086963396088</v>
+        <v>6.030935052050411</v>
       </c>
       <c r="E21" t="n">
-        <v>18.63715480572496</v>
+        <v>21.99443742993778</v>
       </c>
     </row>
   </sheetData>
